--- a/result/first_infection_DA_2023/01_attached_inventory.xlsx
+++ b/result/first_infection_DA_2023/01_attached_inventory.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:B280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>44927</v>
+        <v>45013</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -454,7 +454,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>44928</v>
+        <v>45014</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -462,7 +462,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>44929</v>
+        <v>45015</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -470,15 +470,15 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>44930</v>
+        <v>45016</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.01065307491294137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>44931</v>
+        <v>45017</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -486,7 +486,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>44932</v>
+        <v>45018</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -494,7 +494,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>44933</v>
+        <v>45019</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -502,7 +502,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>44934</v>
+        <v>45020</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -510,15 +510,15 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>44935</v>
+        <v>45021</v>
       </c>
       <c r="B10" t="n">
-        <v>0.006100018058698982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>44936</v>
+        <v>45022</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>44937</v>
+        <v>45023</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -534,7 +534,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>44938</v>
+        <v>45024</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>44939</v>
+        <v>45025</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -550,15 +550,15 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>44940</v>
+        <v>45026</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.01462802194407493</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>44941</v>
+        <v>45027</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>44942</v>
+        <v>45028</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>44943</v>
+        <v>45029</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -582,7 +582,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>44944</v>
+        <v>45030</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>44945</v>
+        <v>45031</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -598,7 +598,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>44946</v>
+        <v>45032</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>44947</v>
+        <v>45033</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
@@ -614,7 +614,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>44948</v>
+        <v>45034</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>44949</v>
+        <v>45035</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>44950</v>
+        <v>45036</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>44951</v>
+        <v>45037</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>44952</v>
+        <v>45038</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -654,7 +654,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>44953</v>
+        <v>45039</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -662,7 +662,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>44954</v>
+        <v>45040</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -670,7 +670,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>44955</v>
+        <v>45041</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -678,7 +678,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>44956</v>
+        <v>45042</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>44957</v>
+        <v>45043</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -694,7 +694,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>44958</v>
+        <v>45044</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>44959</v>
+        <v>45045</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -710,7 +710,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>44960</v>
+        <v>45046</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>44961</v>
+        <v>45047</v>
       </c>
       <c r="B36" t="n">
         <v>0</v>
@@ -726,7 +726,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>44962</v>
+        <v>45048</v>
       </c>
       <c r="B37" t="n">
         <v>0</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>44963</v>
+        <v>45049</v>
       </c>
       <c r="B38" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>44964</v>
+        <v>45050</v>
       </c>
       <c r="B39" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>44965</v>
+        <v>45051</v>
       </c>
       <c r="B40" t="n">
         <v>0</v>
@@ -758,7 +758,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>44966</v>
+        <v>45052</v>
       </c>
       <c r="B41" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>44967</v>
+        <v>45053</v>
       </c>
       <c r="B42" t="n">
         <v>0</v>
@@ -774,7 +774,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>44968</v>
+        <v>45054</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>44969</v>
+        <v>45055</v>
       </c>
       <c r="B44" t="n">
         <v>0</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>44970</v>
+        <v>45056</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>44971</v>
+        <v>45057</v>
       </c>
       <c r="B46" t="n">
         <v>0</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>44972</v>
+        <v>45058</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
@@ -814,7 +814,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>44973</v>
+        <v>45059</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
@@ -822,15 +822,15 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>44974</v>
+        <v>45060</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>0.01392185881714628</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>44975</v>
+        <v>45061</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
@@ -838,7 +838,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>44976</v>
+        <v>45062</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>44977</v>
+        <v>45063</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
@@ -854,7 +854,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>44978</v>
+        <v>45064</v>
       </c>
       <c r="B53" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>44979</v>
+        <v>45065</v>
       </c>
       <c r="B54" t="n">
         <v>0</v>
@@ -870,7 +870,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>44980</v>
+        <v>45066</v>
       </c>
       <c r="B55" t="n">
         <v>0</v>
@@ -878,7 +878,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>44981</v>
+        <v>45067</v>
       </c>
       <c r="B56" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>44982</v>
+        <v>45068</v>
       </c>
       <c r="B57" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>44983</v>
+        <v>45069</v>
       </c>
       <c r="B58" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>44984</v>
+        <v>45070</v>
       </c>
       <c r="B59" t="n">
         <v>0</v>
@@ -910,7 +910,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>44985</v>
+        <v>45071</v>
       </c>
       <c r="B60" t="n">
         <v>0</v>
@@ -918,7 +918,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>44986</v>
+        <v>45072</v>
       </c>
       <c r="B61" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>44987</v>
+        <v>45073</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>44988</v>
+        <v>45074</v>
       </c>
       <c r="B63" t="n">
         <v>0</v>
@@ -942,31 +942,31 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>44989</v>
+        <v>45075</v>
       </c>
       <c r="B64" t="n">
-        <v>0.00370402268733832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>44990</v>
+        <v>45076</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>0.02010170757388014</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>44991</v>
+        <v>45077</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>0.0007169077153621104</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>44992</v>
+        <v>45078</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>44993</v>
+        <v>45079</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
@@ -982,15 +982,15 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>44994</v>
+        <v>45080</v>
       </c>
       <c r="B69" t="n">
-        <v>0.01492855731088964</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>44995</v>
+        <v>45081</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -998,7 +998,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>44996</v>
+        <v>45082</v>
       </c>
       <c r="B71" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>44997</v>
+        <v>45083</v>
       </c>
       <c r="B72" t="n">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>44998</v>
+        <v>45084</v>
       </c>
       <c r="B73" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>44999</v>
+        <v>45085</v>
       </c>
       <c r="B74" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45000</v>
+        <v>45086</v>
       </c>
       <c r="B75" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45001</v>
+        <v>45087</v>
       </c>
       <c r="B76" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45002</v>
+        <v>45088</v>
       </c>
       <c r="B77" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45003</v>
+        <v>45089</v>
       </c>
       <c r="B78" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45004</v>
+        <v>45090</v>
       </c>
       <c r="B79" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45005</v>
+        <v>45091</v>
       </c>
       <c r="B80" t="n">
         <v>0</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45006</v>
+        <v>45092</v>
       </c>
       <c r="B81" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45007</v>
+        <v>45093</v>
       </c>
       <c r="B82" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45008</v>
+        <v>45094</v>
       </c>
       <c r="B83" t="n">
         <v>0</v>
@@ -1102,7 +1102,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45009</v>
+        <v>45095</v>
       </c>
       <c r="B84" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45010</v>
+        <v>45096</v>
       </c>
       <c r="B85" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45011</v>
+        <v>45097</v>
       </c>
       <c r="B86" t="n">
         <v>0</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45012</v>
+        <v>45098</v>
       </c>
       <c r="B87" t="n">
         <v>0</v>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45013</v>
+        <v>45099</v>
       </c>
       <c r="B88" t="n">
         <v>0</v>
@@ -1142,7 +1142,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45014</v>
+        <v>45100</v>
       </c>
       <c r="B89" t="n">
         <v>0</v>
@@ -1150,23 +1150,23 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45015</v>
+        <v>45101</v>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>0.01370726074950828</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45016</v>
+        <v>45102</v>
       </c>
       <c r="B91" t="n">
-        <v>0.01065307491294137</v>
+        <v>0.01577276376226735</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45017</v>
+        <v>45103</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45018</v>
+        <v>45104</v>
       </c>
       <c r="B93" t="n">
         <v>0</v>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45019</v>
+        <v>45105</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45020</v>
+        <v>45106</v>
       </c>
       <c r="B95" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45021</v>
+        <v>45107</v>
       </c>
       <c r="B96" t="n">
         <v>0</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45022</v>
+        <v>45108</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45023</v>
+        <v>45109</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45024</v>
+        <v>45110</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45025</v>
+        <v>45111</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1238,15 +1238,15 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45026</v>
+        <v>45112</v>
       </c>
       <c r="B101" t="n">
-        <v>0.01462802194407493</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45027</v>
+        <v>45113</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45028</v>
+        <v>45114</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45029</v>
+        <v>45115</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45030</v>
+        <v>45116</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45031</v>
+        <v>45117</v>
       </c>
       <c r="B106" t="n">
         <v>0</v>
@@ -1286,7 +1286,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45032</v>
+        <v>45118</v>
       </c>
       <c r="B107" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45033</v>
+        <v>45119</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45034</v>
+        <v>45120</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45035</v>
+        <v>45121</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45036</v>
+        <v>45122</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45037</v>
+        <v>45123</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45038</v>
+        <v>45124</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45039</v>
+        <v>45125</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45040</v>
+        <v>45126</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45041</v>
+        <v>45127</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>45042</v>
+        <v>45128</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>45043</v>
+        <v>45129</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>45044</v>
+        <v>45130</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>45045</v>
+        <v>45131</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>45046</v>
+        <v>45132</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>45047</v>
+        <v>45133</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>45048</v>
+        <v>45134</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>45049</v>
+        <v>45135</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>45050</v>
+        <v>45136</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>45051</v>
+        <v>45137</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -1446,7 +1446,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>45052</v>
+        <v>45138</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>45053</v>
+        <v>45139</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>45054</v>
+        <v>45140</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -1470,15 +1470,15 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>45055</v>
+        <v>45141</v>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>0.01694278175687185</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>45056</v>
+        <v>45142</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>45057</v>
+        <v>45143</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -1494,15 +1494,15 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>45058</v>
+        <v>45144</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>0.01287963570084739</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>45059</v>
+        <v>45145</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -1510,15 +1510,15 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>45060</v>
+        <v>45146</v>
       </c>
       <c r="B135" t="n">
-        <v>0.01392185881714628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>45061</v>
+        <v>45147</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -1526,15 +1526,15 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>45062</v>
+        <v>45148</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>0.01426212893656172</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>45063</v>
+        <v>45149</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -1542,31 +1542,31 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>45064</v>
+        <v>45150</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>0.01540543373988849</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>45065</v>
+        <v>45151</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>0.01489393614721991</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>45066</v>
+        <v>45152</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>0.01436193359083196</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>45067</v>
+        <v>45153</v>
       </c>
       <c r="B142" t="n">
         <v>0</v>
@@ -1574,23 +1574,23 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>45068</v>
+        <v>45154</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>0.01399474339919812</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>45069</v>
+        <v>45155</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>0.01340699762036735</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>45070</v>
+        <v>45156</v>
       </c>
       <c r="B145" t="n">
         <v>0</v>
@@ -1598,15 +1598,15 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>45071</v>
+        <v>45157</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>0.01652245704654333</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>45072</v>
+        <v>45158</v>
       </c>
       <c r="B147" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>45073</v>
+        <v>45159</v>
       </c>
       <c r="B148" t="n">
         <v>0</v>
@@ -1622,15 +1622,15 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>45074</v>
+        <v>45160</v>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>0.01266239817499021</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>45075</v>
+        <v>45161</v>
       </c>
       <c r="B150" t="n">
         <v>0</v>
@@ -1638,23 +1638,23 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>45076</v>
+        <v>45162</v>
       </c>
       <c r="B151" t="n">
-        <v>0.02010170757388014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>45077</v>
+        <v>45163</v>
       </c>
       <c r="B152" t="n">
-        <v>0.0007169077153621104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>45078</v>
+        <v>45164</v>
       </c>
       <c r="B153" t="n">
         <v>0</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>45079</v>
+        <v>45165</v>
       </c>
       <c r="B154" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>45080</v>
+        <v>45166</v>
       </c>
       <c r="B155" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>45081</v>
+        <v>45167</v>
       </c>
       <c r="B156" t="n">
         <v>0</v>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>45082</v>
+        <v>45168</v>
       </c>
       <c r="B157" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>45083</v>
+        <v>45169</v>
       </c>
       <c r="B158" t="n">
         <v>0</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>45084</v>
+        <v>45170</v>
       </c>
       <c r="B159" t="n">
         <v>0</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>45085</v>
+        <v>45171</v>
       </c>
       <c r="B160" t="n">
         <v>0</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>45086</v>
+        <v>45172</v>
       </c>
       <c r="B161" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>45087</v>
+        <v>45173</v>
       </c>
       <c r="B162" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>45088</v>
+        <v>45174</v>
       </c>
       <c r="B163" t="n">
         <v>0</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>45089</v>
+        <v>45175</v>
       </c>
       <c r="B164" t="n">
         <v>0</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>45090</v>
+        <v>45176</v>
       </c>
       <c r="B165" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>45091</v>
+        <v>45177</v>
       </c>
       <c r="B166" t="n">
         <v>0</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>45092</v>
+        <v>45178</v>
       </c>
       <c r="B167" t="n">
         <v>0</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>45093</v>
+        <v>45179</v>
       </c>
       <c r="B168" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>45094</v>
+        <v>45180</v>
       </c>
       <c r="B169" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>45095</v>
+        <v>45181</v>
       </c>
       <c r="B170" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>45096</v>
+        <v>45182</v>
       </c>
       <c r="B171" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>45097</v>
+        <v>45183</v>
       </c>
       <c r="B172" t="n">
         <v>0</v>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>45098</v>
+        <v>45184</v>
       </c>
       <c r="B173" t="n">
         <v>0</v>
@@ -1822,15 +1822,15 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>45099</v>
+        <v>45185</v>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>0.01847505549262613</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>45100</v>
+        <v>45186</v>
       </c>
       <c r="B175" t="n">
         <v>0</v>
@@ -1838,23 +1838,23 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>45101</v>
+        <v>45187</v>
       </c>
       <c r="B176" t="n">
-        <v>0.01370726074950828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>45102</v>
+        <v>45188</v>
       </c>
       <c r="B177" t="n">
-        <v>0.01577276376226735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>45103</v>
+        <v>45189</v>
       </c>
       <c r="B178" t="n">
         <v>0</v>
@@ -1862,15 +1862,15 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>45104</v>
+        <v>45190</v>
       </c>
       <c r="B179" t="n">
-        <v>0</v>
+        <v>0.01524382510427314</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>45105</v>
+        <v>45191</v>
       </c>
       <c r="B180" t="n">
         <v>0</v>
@@ -1878,7 +1878,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>45106</v>
+        <v>45192</v>
       </c>
       <c r="B181" t="n">
         <v>0</v>
@@ -1886,15 +1886,15 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>45107</v>
+        <v>45193</v>
       </c>
       <c r="B182" t="n">
-        <v>0</v>
+        <v>0.01723573818399163</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>45108</v>
+        <v>45194</v>
       </c>
       <c r="B183" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>45109</v>
+        <v>45195</v>
       </c>
       <c r="B184" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>45110</v>
+        <v>45196</v>
       </c>
       <c r="B185" t="n">
         <v>0</v>
@@ -1918,15 +1918,15 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>45111</v>
+        <v>45197</v>
       </c>
       <c r="B186" t="n">
-        <v>0</v>
+        <v>0.01568444314947284</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>45112</v>
+        <v>45198</v>
       </c>
       <c r="B187" t="n">
         <v>0</v>
@@ -1934,15 +1934,15 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>45113</v>
+        <v>45199</v>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>0.01592576059335138</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>45114</v>
+        <v>45200</v>
       </c>
       <c r="B189" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>45115</v>
+        <v>45201</v>
       </c>
       <c r="B190" t="n">
         <v>0</v>
@@ -1958,23 +1958,23 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>45116</v>
+        <v>45202</v>
       </c>
       <c r="B191" t="n">
-        <v>0</v>
+        <v>0.01272329948889638</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>45117</v>
+        <v>45203</v>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>0.01496818920895058</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>45118</v>
+        <v>45204</v>
       </c>
       <c r="B193" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>45119</v>
+        <v>45205</v>
       </c>
       <c r="B194" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>45120</v>
+        <v>45206</v>
       </c>
       <c r="B195" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>45121</v>
+        <v>45207</v>
       </c>
       <c r="B196" t="n">
         <v>0</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>45122</v>
+        <v>45208</v>
       </c>
       <c r="B197" t="n">
         <v>0</v>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>45123</v>
+        <v>45209</v>
       </c>
       <c r="B198" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>45124</v>
+        <v>45210</v>
       </c>
       <c r="B199" t="n">
         <v>0</v>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>45125</v>
+        <v>45211</v>
       </c>
       <c r="B200" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>45126</v>
+        <v>45212</v>
       </c>
       <c r="B201" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>45127</v>
+        <v>45213</v>
       </c>
       <c r="B202" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>45128</v>
+        <v>45214</v>
       </c>
       <c r="B203" t="n">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>45129</v>
+        <v>45215</v>
       </c>
       <c r="B204" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>45130</v>
+        <v>45216</v>
       </c>
       <c r="B205" t="n">
         <v>0</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>45131</v>
+        <v>45217</v>
       </c>
       <c r="B206" t="n">
         <v>0</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>45132</v>
+        <v>45218</v>
       </c>
       <c r="B207" t="n">
         <v>0</v>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>45133</v>
+        <v>45219</v>
       </c>
       <c r="B208" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>45134</v>
+        <v>45220</v>
       </c>
       <c r="B209" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>45135</v>
+        <v>45221</v>
       </c>
       <c r="B210" t="n">
         <v>0</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>45136</v>
+        <v>45222</v>
       </c>
       <c r="B211" t="n">
         <v>0</v>
@@ -2126,15 +2126,15 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>45137</v>
+        <v>45223</v>
       </c>
       <c r="B212" t="n">
-        <v>0</v>
+        <v>0.01605637541235184</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>45138</v>
+        <v>45224</v>
       </c>
       <c r="B213" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>45139</v>
+        <v>45225</v>
       </c>
       <c r="B214" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>45140</v>
+        <v>45226</v>
       </c>
       <c r="B215" t="n">
         <v>0</v>
@@ -2158,15 +2158,15 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>45141</v>
+        <v>45227</v>
       </c>
       <c r="B216" t="n">
-        <v>0.01694278175687185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>45142</v>
+        <v>45228</v>
       </c>
       <c r="B217" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>45143</v>
+        <v>45229</v>
       </c>
       <c r="B218" t="n">
         <v>0</v>
@@ -2182,23 +2182,23 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>45144</v>
+        <v>45230</v>
       </c>
       <c r="B219" t="n">
-        <v>0.01287963570084739</v>
+        <v>0.01456213895253487</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>45145</v>
+        <v>45231</v>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>0.0003813975795300387</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>45146</v>
+        <v>45232</v>
       </c>
       <c r="B221" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>45147</v>
+        <v>45233</v>
       </c>
       <c r="B222" t="n">
         <v>0</v>
@@ -2214,15 +2214,15 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>45148</v>
+        <v>45234</v>
       </c>
       <c r="B223" t="n">
-        <v>0.01426212893656172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>45149</v>
+        <v>45235</v>
       </c>
       <c r="B224" t="n">
         <v>0</v>
@@ -2230,31 +2230,31 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>45150</v>
+        <v>45236</v>
       </c>
       <c r="B225" t="n">
-        <v>0.01540543373988849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>45151</v>
+        <v>45237</v>
       </c>
       <c r="B226" t="n">
-        <v>0.01489393614721991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>45152</v>
+        <v>45238</v>
       </c>
       <c r="B227" t="n">
-        <v>0.01436193359083196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>45153</v>
+        <v>45239</v>
       </c>
       <c r="B228" t="n">
         <v>0</v>
@@ -2262,23 +2262,23 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>45154</v>
+        <v>45240</v>
       </c>
       <c r="B229" t="n">
-        <v>0.01399474339919812</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>45155</v>
+        <v>45241</v>
       </c>
       <c r="B230" t="n">
-        <v>0.01340699762036735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>45156</v>
+        <v>45242</v>
       </c>
       <c r="B231" t="n">
         <v>0</v>
@@ -2286,15 +2286,15 @@
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>45157</v>
+        <v>45243</v>
       </c>
       <c r="B232" t="n">
-        <v>0.01652245704654333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>45158</v>
+        <v>45244</v>
       </c>
       <c r="B233" t="n">
         <v>0</v>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>45159</v>
+        <v>45245</v>
       </c>
       <c r="B234" t="n">
         <v>0</v>
@@ -2310,15 +2310,15 @@
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>45160</v>
+        <v>45246</v>
       </c>
       <c r="B235" t="n">
-        <v>0.01266239817499021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>45161</v>
+        <v>45247</v>
       </c>
       <c r="B236" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>45162</v>
+        <v>45248</v>
       </c>
       <c r="B237" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>45163</v>
+        <v>45249</v>
       </c>
       <c r="B238" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>45164</v>
+        <v>45250</v>
       </c>
       <c r="B239" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>45165</v>
+        <v>45251</v>
       </c>
       <c r="B240" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>45166</v>
+        <v>45252</v>
       </c>
       <c r="B241" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>45167</v>
+        <v>45253</v>
       </c>
       <c r="B242" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>45168</v>
+        <v>45254</v>
       </c>
       <c r="B243" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>45169</v>
+        <v>45255</v>
       </c>
       <c r="B244" t="n">
         <v>0</v>
@@ -2390,31 +2390,31 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>45170</v>
+        <v>45256</v>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>0.009293374928900913</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>45171</v>
+        <v>45257</v>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>0.01356485292149049</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>45172</v>
+        <v>45258</v>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>0.006808012913803386</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>45173</v>
+        <v>45259</v>
       </c>
       <c r="B248" t="n">
         <v>0</v>
@@ -2422,7 +2422,7 @@
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>45174</v>
+        <v>45260</v>
       </c>
       <c r="B249" t="n">
         <v>0</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>45175</v>
+        <v>45261</v>
       </c>
       <c r="B250" t="n">
         <v>0</v>
@@ -2438,7 +2438,7 @@
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>45176</v>
+        <v>45262</v>
       </c>
       <c r="B251" t="n">
         <v>0</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>45177</v>
+        <v>45263</v>
       </c>
       <c r="B252" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>45178</v>
+        <v>45264</v>
       </c>
       <c r="B253" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>45179</v>
+        <v>45265</v>
       </c>
       <c r="B254" t="n">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>45180</v>
+        <v>45266</v>
       </c>
       <c r="B255" t="n">
         <v>0</v>
@@ -2478,15 +2478,15 @@
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>45181</v>
+        <v>45267</v>
       </c>
       <c r="B256" t="n">
-        <v>0</v>
+        <v>0.002037844003953508</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>45182</v>
+        <v>45268</v>
       </c>
       <c r="B257" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>45183</v>
+        <v>45269</v>
       </c>
       <c r="B258" t="n">
         <v>0</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>45184</v>
+        <v>45270</v>
       </c>
       <c r="B259" t="n">
         <v>0</v>
@@ -2510,15 +2510,15 @@
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>45185</v>
+        <v>45271</v>
       </c>
       <c r="B260" t="n">
-        <v>0.01847505549262613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>45186</v>
+        <v>45272</v>
       </c>
       <c r="B261" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>45187</v>
+        <v>45273</v>
       </c>
       <c r="B262" t="n">
         <v>0</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>45188</v>
+        <v>45274</v>
       </c>
       <c r="B263" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>45189</v>
+        <v>45275</v>
       </c>
       <c r="B264" t="n">
         <v>0</v>
@@ -2550,15 +2550,15 @@
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>45190</v>
+        <v>45276</v>
       </c>
       <c r="B265" t="n">
-        <v>0.01524382510427314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>45191</v>
+        <v>45277</v>
       </c>
       <c r="B266" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>45192</v>
+        <v>45278</v>
       </c>
       <c r="B267" t="n">
         <v>0</v>
@@ -2574,15 +2574,15 @@
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>45193</v>
+        <v>45279</v>
       </c>
       <c r="B268" t="n">
-        <v>0.01723573818399163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
-        <v>45194</v>
+        <v>45280</v>
       </c>
       <c r="B269" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
-        <v>45195</v>
+        <v>45281</v>
       </c>
       <c r="B270" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
-        <v>45196</v>
+        <v>45282</v>
       </c>
       <c r="B271" t="n">
         <v>0</v>
@@ -2606,15 +2606,15 @@
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
-        <v>45197</v>
+        <v>45283</v>
       </c>
       <c r="B272" t="n">
-        <v>0.01568444314947284</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
-        <v>45198</v>
+        <v>45284</v>
       </c>
       <c r="B273" t="n">
         <v>0</v>
@@ -2622,15 +2622,15 @@
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
-        <v>45199</v>
+        <v>45285</v>
       </c>
       <c r="B274" t="n">
-        <v>0.01592576059335138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
-        <v>45200</v>
+        <v>45286</v>
       </c>
       <c r="B275" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
-        <v>45201</v>
+        <v>45287</v>
       </c>
       <c r="B276" t="n">
         <v>0</v>
@@ -2646,721 +2646,33 @@
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
-        <v>45202</v>
+        <v>45288</v>
       </c>
       <c r="B277" t="n">
-        <v>0.01272329948889638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
-        <v>45203</v>
+        <v>45289</v>
       </c>
       <c r="B278" t="n">
-        <v>0.01496818920895058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
-        <v>45204</v>
+        <v>45290</v>
       </c>
       <c r="B279" t="n">
-        <v>0</v>
+        <v>0.007732480559077315</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
-        <v>45205</v>
+        <v>45291</v>
       </c>
       <c r="B280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="n">
-        <v>45206</v>
-      </c>
-      <c r="B281" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="n">
-        <v>45207</v>
-      </c>
-      <c r="B282" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="n">
-        <v>45208</v>
-      </c>
-      <c r="B283" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="n">
-        <v>45209</v>
-      </c>
-      <c r="B284" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="2" t="n">
-        <v>45210</v>
-      </c>
-      <c r="B285" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="2" t="n">
-        <v>45211</v>
-      </c>
-      <c r="B286" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="n">
-        <v>45212</v>
-      </c>
-      <c r="B287" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="n">
-        <v>45213</v>
-      </c>
-      <c r="B288" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="2" t="n">
-        <v>45214</v>
-      </c>
-      <c r="B289" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="n">
-        <v>45215</v>
-      </c>
-      <c r="B290" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="2" t="n">
-        <v>45216</v>
-      </c>
-      <c r="B291" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="2" t="n">
-        <v>45217</v>
-      </c>
-      <c r="B292" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="n">
-        <v>45218</v>
-      </c>
-      <c r="B293" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="n">
-        <v>45219</v>
-      </c>
-      <c r="B294" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="2" t="n">
-        <v>45220</v>
-      </c>
-      <c r="B295" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="2" t="n">
-        <v>45221</v>
-      </c>
-      <c r="B296" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="n">
-        <v>45222</v>
-      </c>
-      <c r="B297" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="n">
-        <v>45223</v>
-      </c>
-      <c r="B298" t="n">
-        <v>0.01605637541235184</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="n">
-        <v>45224</v>
-      </c>
-      <c r="B299" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="n">
-        <v>45225</v>
-      </c>
-      <c r="B300" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="n">
-        <v>45226</v>
-      </c>
-      <c r="B301" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="n">
-        <v>45227</v>
-      </c>
-      <c r="B302" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="n">
-        <v>45228</v>
-      </c>
-      <c r="B303" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="n">
-        <v>45229</v>
-      </c>
-      <c r="B304" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="n">
-        <v>45230</v>
-      </c>
-      <c r="B305" t="n">
-        <v>0.01456213895253487</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="2" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B306" t="n">
-        <v>0.0003813975795300387</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="n">
-        <v>45232</v>
-      </c>
-      <c r="B307" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="n">
-        <v>45233</v>
-      </c>
-      <c r="B308" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="n">
-        <v>45234</v>
-      </c>
-      <c r="B309" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="n">
-        <v>45235</v>
-      </c>
-      <c r="B310" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="n">
-        <v>45236</v>
-      </c>
-      <c r="B311" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="n">
-        <v>45237</v>
-      </c>
-      <c r="B312" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="n">
-        <v>45238</v>
-      </c>
-      <c r="B313" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="n">
-        <v>45239</v>
-      </c>
-      <c r="B314" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="n">
-        <v>45240</v>
-      </c>
-      <c r="B315" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="n">
-        <v>45241</v>
-      </c>
-      <c r="B316" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="n">
-        <v>45242</v>
-      </c>
-      <c r="B317" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="n">
-        <v>45243</v>
-      </c>
-      <c r="B318" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="n">
-        <v>45244</v>
-      </c>
-      <c r="B319" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="n">
-        <v>45245</v>
-      </c>
-      <c r="B320" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="n">
-        <v>45246</v>
-      </c>
-      <c r="B321" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="n">
-        <v>45247</v>
-      </c>
-      <c r="B322" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="n">
-        <v>45248</v>
-      </c>
-      <c r="B323" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="n">
-        <v>45249</v>
-      </c>
-      <c r="B324" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="B325" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="2" t="n">
-        <v>45251</v>
-      </c>
-      <c r="B326" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="2" t="n">
-        <v>45252</v>
-      </c>
-      <c r="B327" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="2" t="n">
-        <v>45253</v>
-      </c>
-      <c r="B328" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2" t="n">
-        <v>45254</v>
-      </c>
-      <c r="B329" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="2" t="n">
-        <v>45255</v>
-      </c>
-      <c r="B330" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="n">
-        <v>45256</v>
-      </c>
-      <c r="B331" t="n">
-        <v>0.009293374928900913</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="n">
-        <v>45257</v>
-      </c>
-      <c r="B332" t="n">
-        <v>0.01356485292149049</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="n">
-        <v>45258</v>
-      </c>
-      <c r="B333" t="n">
-        <v>0.006808012913803386</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="n">
-        <v>45259</v>
-      </c>
-      <c r="B334" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="n">
-        <v>45260</v>
-      </c>
-      <c r="B335" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B336" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="n">
-        <v>45262</v>
-      </c>
-      <c r="B337" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="n">
-        <v>45263</v>
-      </c>
-      <c r="B338" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="n">
-        <v>45264</v>
-      </c>
-      <c r="B339" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="2" t="n">
-        <v>45265</v>
-      </c>
-      <c r="B340" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="2" t="n">
-        <v>45266</v>
-      </c>
-      <c r="B341" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="2" t="n">
-        <v>45267</v>
-      </c>
-      <c r="B342" t="n">
-        <v>0.002037844003953508</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="2" t="n">
-        <v>45268</v>
-      </c>
-      <c r="B343" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="2" t="n">
-        <v>45269</v>
-      </c>
-      <c r="B344" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="2" t="n">
-        <v>45270</v>
-      </c>
-      <c r="B345" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="2" t="n">
-        <v>45271</v>
-      </c>
-      <c r="B346" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="2" t="n">
-        <v>45272</v>
-      </c>
-      <c r="B347" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="2" t="n">
-        <v>45273</v>
-      </c>
-      <c r="B348" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="2" t="n">
-        <v>45274</v>
-      </c>
-      <c r="B349" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="2" t="n">
-        <v>45275</v>
-      </c>
-      <c r="B350" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="2" t="n">
-        <v>45276</v>
-      </c>
-      <c r="B351" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="2" t="n">
-        <v>45277</v>
-      </c>
-      <c r="B352" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="2" t="n">
-        <v>45278</v>
-      </c>
-      <c r="B353" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="2" t="n">
-        <v>45279</v>
-      </c>
-      <c r="B354" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="2" t="n">
-        <v>45280</v>
-      </c>
-      <c r="B355" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="2" t="n">
-        <v>45281</v>
-      </c>
-      <c r="B356" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="2" t="n">
-        <v>45282</v>
-      </c>
-      <c r="B357" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="2" t="n">
-        <v>45283</v>
-      </c>
-      <c r="B358" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="2" t="n">
-        <v>45284</v>
-      </c>
-      <c r="B359" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="2" t="n">
-        <v>45285</v>
-      </c>
-      <c r="B360" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="2" t="n">
-        <v>45286</v>
-      </c>
-      <c r="B361" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="2" t="n">
-        <v>45287</v>
-      </c>
-      <c r="B362" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="2" t="n">
-        <v>45288</v>
-      </c>
-      <c r="B363" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="2" t="n">
-        <v>45289</v>
-      </c>
-      <c r="B364" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="2" t="n">
-        <v>45290</v>
-      </c>
-      <c r="B365" t="n">
-        <v>0.007732480559077315</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="2" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B366" t="n">
         <v>0</v>
       </c>
     </row>

--- a/result/first_infection_DA_2023/01_attached_inventory.xlsx
+++ b/result/first_infection_DA_2023/01_attached_inventory.xlsx
@@ -473,7 +473,7 @@
         <v>45016</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01065307491294137</v>
+        <v>0.01693476260834023</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         <v>45059</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>0.01581212424234987</v>
       </c>
     </row>
     <row r="49">
@@ -825,7 +825,7 @@
         <v>45060</v>
       </c>
       <c r="B49" t="n">
-        <v>0.01392185881714628</v>
+        <v>0.01714089340128684</v>
       </c>
     </row>
     <row r="50">
@@ -953,7 +953,7 @@
         <v>45076</v>
       </c>
       <c r="B65" t="n">
-        <v>0.02010170757388014</v>
+        <v>0.02120319080501113</v>
       </c>
     </row>
     <row r="66">
@@ -961,7 +961,7 @@
         <v>45077</v>
       </c>
       <c r="B66" t="n">
-        <v>0.0007169077153621104</v>
+        <v>0.02117423402753322</v>
       </c>
     </row>
     <row r="67">
@@ -1057,7 +1057,7 @@
         <v>45089</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>0.0143809353645617</v>
       </c>
     </row>
     <row r="79">
@@ -1417,7 +1417,7 @@
         <v>45134</v>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>0.01534636965639627</v>
       </c>
     </row>
     <row r="124">
@@ -1473,7 +1473,7 @@
         <v>45141</v>
       </c>
       <c r="B130" t="n">
-        <v>0.01694278175687185</v>
+        <v>0.01710630670524918</v>
       </c>
     </row>
     <row r="131">
@@ -1529,7 +1529,7 @@
         <v>45148</v>
       </c>
       <c r="B137" t="n">
-        <v>0.01426212893656172</v>
+        <v>0.01434130344066498</v>
       </c>
     </row>
     <row r="138">
@@ -1545,7 +1545,7 @@
         <v>45150</v>
       </c>
       <c r="B139" t="n">
-        <v>0.01540543373988849</v>
+        <v>0.01610314121000416</v>
       </c>
     </row>
     <row r="140">
@@ -1553,7 +1553,7 @@
         <v>45151</v>
       </c>
       <c r="B140" t="n">
-        <v>0.01489393614721991</v>
+        <v>0.01530238605616763</v>
       </c>
     </row>
     <row r="141">
@@ -1561,7 +1561,7 @@
         <v>45152</v>
       </c>
       <c r="B141" t="n">
-        <v>0.01436193359083196</v>
+        <v>0.01495153281655307</v>
       </c>
     </row>
     <row r="142">
@@ -1577,7 +1577,7 @@
         <v>45154</v>
       </c>
       <c r="B143" t="n">
-        <v>0.01399474339919812</v>
+        <v>0.01429252018782793</v>
       </c>
     </row>
     <row r="144">
@@ -1585,7 +1585,7 @@
         <v>45155</v>
       </c>
       <c r="B144" t="n">
-        <v>0.01340699762036735</v>
+        <v>0.01377694039578724</v>
       </c>
     </row>
     <row r="145">
@@ -1625,7 +1625,7 @@
         <v>45160</v>
       </c>
       <c r="B149" t="n">
-        <v>0.01266239817499021</v>
+        <v>0.0129419056541528</v>
       </c>
     </row>
     <row r="150">
@@ -1825,7 +1825,7 @@
         <v>45185</v>
       </c>
       <c r="B174" t="n">
-        <v>0.01847505549262613</v>
+        <v>0.01864543307605041</v>
       </c>
     </row>
     <row r="175">
@@ -1865,7 +1865,7 @@
         <v>45190</v>
       </c>
       <c r="B179" t="n">
-        <v>0.01524382510427314</v>
+        <v>0.01520803512090434</v>
       </c>
     </row>
     <row r="180">
@@ -1889,7 +1889,7 @@
         <v>45193</v>
       </c>
       <c r="B182" t="n">
-        <v>0.01723573818399163</v>
+        <v>0.01835498528958714</v>
       </c>
     </row>
     <row r="183">
@@ -1921,7 +1921,7 @@
         <v>45197</v>
       </c>
       <c r="B186" t="n">
-        <v>0.01568444314947284</v>
+        <v>0.01625997905876253</v>
       </c>
     </row>
     <row r="187">
@@ -1937,7 +1937,7 @@
         <v>45199</v>
       </c>
       <c r="B188" t="n">
-        <v>0.01592576059335138</v>
+        <v>0.01646421388233836</v>
       </c>
     </row>
     <row r="189">
@@ -1961,7 +1961,7 @@
         <v>45202</v>
       </c>
       <c r="B191" t="n">
-        <v>0.01272329948889638</v>
+        <v>0.01599941624413282</v>
       </c>
     </row>
     <row r="192">
@@ -1969,7 +1969,7 @@
         <v>45203</v>
       </c>
       <c r="B192" t="n">
-        <v>0.01496818920895058</v>
+        <v>0.01690013766266251</v>
       </c>
     </row>
     <row r="193">
@@ -2033,7 +2033,7 @@
         <v>45211</v>
       </c>
       <c r="B200" t="n">
-        <v>0</v>
+        <v>0.0127392016431254</v>
       </c>
     </row>
     <row r="201">
@@ -2065,7 +2065,7 @@
         <v>45215</v>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>0.02485271951903046</v>
       </c>
     </row>
     <row r="205">
@@ -2129,7 +2129,7 @@
         <v>45223</v>
       </c>
       <c r="B212" t="n">
-        <v>0.01605637541235184</v>
+        <v>0.02299662161816616</v>
       </c>
     </row>
     <row r="213">
@@ -2185,7 +2185,7 @@
         <v>45230</v>
       </c>
       <c r="B219" t="n">
-        <v>0.01456213895253487</v>
+        <v>0.02081772846847346</v>
       </c>
     </row>
     <row r="220">
@@ -2193,7 +2193,7 @@
         <v>45231</v>
       </c>
       <c r="B220" t="n">
-        <v>0.0003813975795300387</v>
+        <v>0.01795597076616553</v>
       </c>
     </row>
     <row r="221">
@@ -2329,7 +2329,7 @@
         <v>45248</v>
       </c>
       <c r="B237" t="n">
-        <v>0</v>
+        <v>0.001445973614669436</v>
       </c>
     </row>
     <row r="238">
@@ -2337,7 +2337,7 @@
         <v>45249</v>
       </c>
       <c r="B238" t="n">
-        <v>0</v>
+        <v>3.682575213814048e-05</v>
       </c>
     </row>
     <row r="239">
@@ -2345,7 +2345,7 @@
         <v>45250</v>
       </c>
       <c r="B239" t="n">
-        <v>0</v>
+        <v>9.240154971918502e-07</v>
       </c>
     </row>
     <row r="240">
@@ -2353,7 +2353,7 @@
         <v>45251</v>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>2.206815900422882e-08</v>
       </c>
     </row>
     <row r="241">
@@ -2361,7 +2361,7 @@
         <v>45252</v>
       </c>
       <c r="B241" t="n">
-        <v>0</v>
+        <v>0.01447480371070392</v>
       </c>
     </row>
     <row r="242">
@@ -2393,7 +2393,7 @@
         <v>45256</v>
       </c>
       <c r="B245" t="n">
-        <v>0.009293374928900913</v>
+        <v>0.01760372453386309</v>
       </c>
     </row>
     <row r="246">
@@ -2401,7 +2401,7 @@
         <v>45257</v>
       </c>
       <c r="B246" t="n">
-        <v>0.01356485292149049</v>
+        <v>0.014846107520369</v>
       </c>
     </row>
     <row r="247">
@@ -2409,7 +2409,7 @@
         <v>45258</v>
       </c>
       <c r="B247" t="n">
-        <v>0.006808012913803386</v>
+        <v>0.006840504999747295</v>
       </c>
     </row>
     <row r="248">
@@ -2449,7 +2449,7 @@
         <v>45263</v>
       </c>
       <c r="B252" t="n">
-        <v>0</v>
+        <v>0.005949137511067324</v>
       </c>
     </row>
     <row r="253">
@@ -2481,7 +2481,7 @@
         <v>45267</v>
       </c>
       <c r="B256" t="n">
-        <v>0.002037844003953508</v>
+        <v>0.004088657127467837</v>
       </c>
     </row>
     <row r="257">
@@ -2665,7 +2665,7 @@
         <v>45290</v>
       </c>
       <c r="B279" t="n">
-        <v>0.007732480559077315</v>
+        <v>0.01550775821435383</v>
       </c>
     </row>
     <row r="280">
